--- a/companies/meridian-actuarial/Finance/FY2020 Financial Summary.xlsx
+++ b/companies/meridian-actuarial/Finance/FY2020 Financial Summary.xlsx
@@ -474,20 +474,20 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>626128</v>
+        <v>647258</v>
       </c>
       <c r="C4" s="3">
-        <v>527425</v>
+        <v>441372</v>
       </c>
       <c r="D4" s="3">
-        <v>658398</v>
+        <v>615797</v>
       </c>
       <c r="E4" s="3">
-        <v>483049</v>
+        <v>475573</v>
       </c>
       <c r="F4" s="4">
         <f>SUM(B4:E4)</f>
-        <v>2295000</v>
+        <v>2180000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>148180</v>
+        <v>35190</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>1705850</v>
+        <v>1592860</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>589150</v>
+        <v>587140</v>
       </c>
     </row>
   </sheetData>
